--- a/public/storage/souvenirUsers.xlsx
+++ b/public/storage/souvenirUsers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\mpu-crm\storage\app\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josechan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F79614E-616B-43B4-8E0E-69B8D4377C90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265EDF7E-30F1-43F8-8EF4-BEF4B3F46993}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12120" windowHeight="24705" xr2:uid="{F3E07AF1-43BB-432F-9739-45A146350FEC}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12120" windowHeight="16890" xr2:uid="{F3E07AF1-43BB-432F-9739-45A146350FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>p2000020@mpu.edu.mo</t>
   </si>
@@ -49,12 +49,6 @@
     <t>can_buy</t>
   </si>
   <si>
-    <t>name_zh</t>
-  </si>
-  <si>
-    <t>name_en</t>
-  </si>
-  <si>
     <t>p200003@mpu.edu.mo</t>
   </si>
   <si>
@@ -64,12 +58,6 @@
     <t>name_zh_2</t>
   </si>
   <si>
-    <t>name_en_1</t>
-  </si>
-  <si>
-    <t>name_en_2</t>
-  </si>
-  <si>
     <t>F1</t>
   </si>
   <si>
@@ -113,6 +101,9 @@
   </si>
   <si>
     <t>grad_year</t>
+  </si>
+  <si>
+    <t>name</t>
   </si>
 </sst>
 </file>
@@ -497,117 +488,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E31CAC-3C40-4D14-82F7-1DA70453B9DC}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>64562102</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="2">
+        <v>61231546</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="3">
         <v>0</v>
       </c>
-      <c r="E2" s="2">
-        <v>64562102</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="3">
-        <v>2026</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
-        <v>61231546</v>
-      </c>
-      <c r="F3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2026</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
+      <c r="H4" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -616,11 +597,10 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{C8977364-155D-40BF-BA0A-D147C60657C6}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{C8977364-155D-40BF-BA0A-D147C60657C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -636,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,7 +624,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -652,7 +632,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -660,7 +640,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -668,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -676,7 +656,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
